--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -527,17 +527,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 19/08/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 21/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -547,17 +547,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 21/08/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -567,17 +567,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 26/08/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 28/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -587,17 +587,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 01/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -607,17 +607,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -627,17 +627,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 08/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -667,17 +667,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -687,17 +687,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 16/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -707,21 +707,21 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 21/09/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -737,7 +737,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 22/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -767,17 +767,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 05/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -787,21 +787,21 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 21/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -827,37 +827,37 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 2º tempo</t>
+          <t>Quarta, 28/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 05/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -887,17 +887,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 13/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -907,21 +907,21 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 18/11/2026 — 3º tempo</t>
+          <t>Quarta, 18/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -980,17 +980,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 19/08/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 21/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -1000,17 +1000,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 21/08/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1020,17 +1020,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 26/08/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 28/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -1040,17 +1040,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 01/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -1060,17 +1060,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -1080,17 +1080,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 08/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1120,17 +1120,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -1140,17 +1140,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 16/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -1160,21 +1160,21 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 21/09/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 22/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -1220,17 +1220,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 05/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -1240,21 +1240,21 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 21/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1280,37 +1280,37 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 2º tempo</t>
+          <t>Quarta, 28/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 05/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -1340,17 +1340,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 13/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -1360,21 +1360,21 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 18/11/2026 — 3º tempo</t>
+          <t>Quarta, 18/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1433,17 +1433,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 17/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 18/08/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -1453,17 +1453,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 19/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1473,17 +1473,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 21/08/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 21/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -1493,37 +1493,37 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 24/08/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 26/08/2026 — 2º e 3º tempos</t>
+          <t>Terça, 25/08/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -1533,17 +1533,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 27/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1553,37 +1553,37 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 1º ao 3º tempos</t>
+          <t>Quarta, 02/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 3º e 4º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -1593,17 +1593,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -1613,17 +1613,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -1653,17 +1653,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 18/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -1673,17 +1673,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 10º e 11º tempos</t>
+          <t>Segunda, 21/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -1693,17 +1693,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 29/09/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -1713,17 +1713,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 01/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 07/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -1733,17 +1733,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 3º e 4º tempos</t>
+          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -1753,57 +1753,57 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 21/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 23/10/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Terça, 27/10/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 28/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -1813,37 +1813,37 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 5º tempo</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -1853,41 +1853,41 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 1º tempo</t>
+          <t>Segunda, 09/11/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 9º ao 11º tempos</t>
+          <t>Quinta, 12/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1946,17 +1946,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 17/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 18/08/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -1966,17 +1966,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 19/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1986,17 +1986,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 21/08/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 21/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -2006,37 +2006,37 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 24/08/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 26/08/2026 — 2º e 3º tempos</t>
+          <t>Terça, 25/08/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -2046,17 +2046,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -2066,37 +2066,37 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 1º ao 3º tempos</t>
+          <t>Quarta, 02/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -2106,17 +2106,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -2126,17 +2126,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -2166,17 +2166,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 18/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -2186,17 +2186,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 10º e 11º tempos</t>
+          <t>Segunda, 21/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -2206,17 +2206,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 29/09/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -2226,17 +2226,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 07/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -2246,17 +2246,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 01/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -2266,41 +2266,41 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 3º e 4º tempos</t>
+          <t>Quarta, 21/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 23/10/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 28/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -2326,17 +2326,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 27/10/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -2346,61 +2346,61 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 5º tempo</t>
+          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 1º tempo</t>
+          <t>Segunda, 09/11/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 9º ao 11º tempos</t>
+          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2459,17 +2459,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 17/08/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 17/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -2479,17 +2479,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 19/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -2499,17 +2499,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 20/08/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 20/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -2519,21 +2519,21 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 1º ao 3º tempos</t>
+          <t>Segunda, 24/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -2559,17 +2559,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 31/08/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -2599,21 +2599,21 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -2639,17 +2639,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 09/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -2659,17 +2659,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -2679,57 +2679,57 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 9º tempo</t>
+          <t>Terça, 15/09/2026 — 8º ao 10º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 18/09/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 21/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -2739,17 +2739,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 01/10/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 28/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -2759,17 +2759,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 01/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -2779,37 +2779,37 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 4º tempo</t>
+          <t>Terça, 06/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 07/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -2819,21 +2819,21 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 21/10/2026 — 9º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2859,17 +2859,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 9º e 10º tempos</t>
+          <t>Terça, 03/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -2879,17 +2879,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 10/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -2899,37 +2899,37 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 9º ao 11º tempos</t>
+          <t>Quinta, 12/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 8º e 9º tempos</t>
+          <t>Quarta, 18/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
@@ -2992,17 +2992,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 17/08/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 17/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -3012,17 +3012,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 19/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -3032,17 +3032,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 20/08/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 20/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -3052,21 +3052,21 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 1º ao 3º tempos</t>
+          <t>Segunda, 24/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3092,17 +3092,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -3112,21 +3112,21 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -3172,17 +3172,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 09/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -3192,17 +3192,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -3212,57 +3212,57 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 9º tempo</t>
+          <t>Terça, 15/09/2026 — 8º ao 10º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 18/09/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 21/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -3292,17 +3292,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 06/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -3312,21 +3312,21 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 4º tempo</t>
+          <t>Quarta, 07/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -3352,21 +3352,21 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 21/10/2026 — 9º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -3392,17 +3392,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 9º e 10º tempos</t>
+          <t>Terça, 03/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -3412,17 +3412,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 10/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -3432,37 +3432,37 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 9º ao 11º tempos</t>
+          <t>Quinta, 12/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 8º e 9º tempos</t>
+          <t>Quarta, 18/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
@@ -3525,17 +3525,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 17/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -3545,17 +3545,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 20/08/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 19/08/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -3565,37 +3565,37 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 21/08/2026 — 1º e 2º tempos</t>
+          <t>Terça, 25/08/2026 — 10º ao 12º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 27/08/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -3605,17 +3605,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 9º e 10º tempos</t>
+          <t>Segunda, 31/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -3625,37 +3625,37 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 1º ao 3º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 04/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -3665,17 +3665,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -3685,17 +3685,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -3705,17 +3705,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -3745,17 +3745,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Terça, 22/09/2026 — 11º e 12º tempos</t>
+          <t>Terça, 22/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -3785,21 +3785,21 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 10º ao 12º tempos</t>
+          <t>Terça, 29/09/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 4º tempo</t>
+          <t>Quarta, 30/09/2026 — 10º tempo</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -3825,17 +3825,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 07/10/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -3845,17 +3845,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 19/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -3885,52 +3885,52 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 21/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 2º tempo</t>
+          <t>Sexta, 30/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -3945,17 +3945,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -3965,17 +3965,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 9º e 10º tempos</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -4038,17 +4038,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 17/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -4058,17 +4058,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 20/08/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 19/08/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -4078,37 +4078,37 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 21/08/2026 — 1º e 2º tempos</t>
+          <t>Terça, 25/08/2026 — 10º ao 12º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 27/08/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -4118,17 +4118,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 9º e 10º tempos</t>
+          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -4138,37 +4138,37 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 1º ao 3º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 04/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -4178,17 +4178,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -4198,17 +4198,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -4218,17 +4218,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -4238,57 +4238,57 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>S4-12</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 16/09 e Quinta, 17/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>S4-12</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 16/09 e Quinta, 17/09/2026 — 2º ao 7º tempos</t>
+          <t>Terça, 22/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Terça, 22/09/2026 — 11º e 12º tempos</t>
+          <t>Sexta, 25/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -4298,17 +4298,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 28/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -4318,21 +4318,21 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 10º ao 12º tempos</t>
+          <t>Terça, 29/09/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 4º tempo</t>
+          <t>Quarta, 30/09/2026 — 10º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -4358,17 +4358,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 07/10/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -4378,17 +4378,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 19/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 2º tempo</t>
+          <t>Quarta, 21/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -4438,37 +4438,37 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 30/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 03/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -4478,17 +4478,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 9º e 10º tempos</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -527,17 +527,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 21/08/2026 — 2º e 3º tempos</t>
+          <t>Terça, 18/08/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -547,17 +547,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 19/08/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -567,17 +567,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 25/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -587,17 +587,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 9º e 10º tempos</t>
+          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -627,17 +627,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 04/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -647,17 +647,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Terça, 08/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -667,17 +667,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -687,17 +687,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -717,7 +717,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 1º tempo</t>
+          <t>Quarta, 23/09/2026 — 3º tempo</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -727,17 +727,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Terça, 22/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 25/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -767,57 +767,57 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 05/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º tempo</t>
+          <t>Quarta, 07/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -827,17 +827,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -847,57 +847,57 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 28/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 2º tempo</t>
+          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 13/11/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 11/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -907,17 +907,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 18/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 19/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -980,17 +980,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 21/08/2026 — 2º e 3º tempos</t>
+          <t>Terça, 18/08/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -1000,17 +1000,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 19/08/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1020,17 +1020,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 25/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -1040,17 +1040,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 9º e 10º tempos</t>
+          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -1080,17 +1080,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 04/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1100,17 +1100,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Terça, 08/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1120,17 +1120,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -1140,17 +1140,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 1º tempo</t>
+          <t>Quarta, 23/09/2026 — 3º tempo</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -1180,17 +1180,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Terça, 22/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 25/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -1220,57 +1220,57 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 05/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º tempo</t>
+          <t>Quarta, 07/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -1280,17 +1280,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -1300,57 +1300,57 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 28/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 2º tempo</t>
+          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 13/11/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 11/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -1360,17 +1360,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 18/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 19/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1653,37 +1653,37 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 18/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 16/09/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 22/09/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -1693,37 +1693,37 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 10º e 11º tempos</t>
+          <t>Sexta, 25/09/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 01/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -1733,17 +1733,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Quinta, 08/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -1753,57 +1753,57 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 1º tempo</t>
+          <t>Segunda, 19/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 5º tempo</t>
+          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 30/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -1813,17 +1813,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -2166,37 +2166,37 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 18/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 16/09/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 22/09/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -2206,37 +2206,37 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 10º e 11º tempos</t>
+          <t>Sexta, 25/09/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 30/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Quinta, 01/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -2266,57 +2266,57 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 1º tempo</t>
+          <t>Quinta, 08/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 5º tempo</t>
+          <t>Segunda, 19/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -2326,17 +2326,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 30/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -2346,17 +2346,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -2366,41 +2366,41 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 1º ao 3º tempos</t>
+          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 09/11/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2459,17 +2459,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 17/08/2026 — 1º e 2º tempos</t>
+          <t>Terça, 18/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -2479,17 +2479,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 19/08/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 19/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -2499,12 +2499,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2519,17 +2519,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 24/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -2559,17 +2559,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -2579,17 +2579,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2599,21 +2599,21 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
+          <t>Terça, 01/09/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 02/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -2639,17 +2639,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 08/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -2659,77 +2659,77 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 10/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 8º ao 10º tempos</t>
+          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 18/09/2026 — 4º tempo</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 24/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -2759,17 +2759,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 01/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 29/09/2026 — 3º e 4º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -2779,137 +2779,137 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 9º e 10º tempos</t>
+          <t>Segunda, 05/10/2026 — 3º ao 5º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 07/10/2026 — 9º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 9º tempo</t>
+          <t>Segunda, 19/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>S4-11</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>S4-11</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 06/11/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 2º e 3º tempos</t>
+          <t>Terça, 10/11/2026 — 8º e 9º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 18/11/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 16/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
@@ -2992,17 +2992,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 17/08/2026 — 1º e 2º tempos</t>
+          <t>Terça, 18/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -3012,17 +3012,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 19/08/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 19/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -3032,17 +3032,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 20/08/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 24/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -3052,57 +3052,57 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>S3-11</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 2º e 3º tempos</t>
+          <t>Terça, 25/08 e Quarta, 26/08/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>S3-11</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08 e Quarta, 26/08/2026 — 2º ao 7º tempos</t>
+          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -3112,37 +3112,37 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
+          <t>Terça, 01/09/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 02/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -3152,17 +3152,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 08/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -3172,37 +3172,37 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 10/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 11/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -3212,57 +3212,57 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 8º ao 10º tempos</t>
+          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 18/09/2026 — 4º tempo</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 24/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -3272,17 +3272,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 01/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 29/09/2026 — 3º e 4º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -3292,57 +3292,57 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 9º e 10º tempos</t>
+          <t>Segunda, 05/10/2026 — 3º ao 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 07/10/2026 — 9º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 19/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -3352,21 +3352,21 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 9º tempo</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -3392,37 +3392,37 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 06/11/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -3432,17 +3432,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 2º e 3º tempos</t>
+          <t>Terça, 10/11/2026 — 8º e 9º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 18/11/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 16/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
@@ -3525,37 +3525,37 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 17/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 18/08/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 19/08/2026 — 11º e 12º tempos</t>
+          <t>Quinta, 20/08/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -3565,37 +3565,37 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 10º ao 12º tempos</t>
+          <t>Segunda, 24/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 9º e 10º tempos</t>
+          <t>Terça, 25/08/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -3605,17 +3605,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 28/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -3625,17 +3625,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -3645,17 +3645,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -3705,12 +3705,12 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Terça, 22/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 24/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -3765,17 +3765,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 25/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -3785,17 +3785,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 11º e 12º tempos</t>
+          <t>Terça, 29/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -3805,37 +3805,37 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 10º tempo</t>
+          <t>Segunda, 05/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 11º e 12º tempos</t>
+          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -3845,37 +3845,37 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Terça, 20/10/2026 — 11º ao 13º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 26/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -3885,17 +3885,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º tempo</t>
+          <t>Quarta, 28/10/2026 — 10º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -3905,37 +3905,37 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 1º ao 3º tempos</t>
+          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -3945,37 +3945,37 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 11/11/2026 — 6º tempo</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 12/11/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -4038,37 +4038,37 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 17/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 18/08/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 19/08/2026 — 11º e 12º tempos</t>
+          <t>Quinta, 20/08/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -4078,37 +4078,37 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 10º ao 12º tempos</t>
+          <t>Segunda, 24/08/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 9º e 10º tempos</t>
+          <t>Terça, 25/08/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -4118,17 +4118,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 28/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -4138,17 +4138,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -4158,17 +4158,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -4218,12 +4218,12 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Terça, 22/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 24/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -4278,17 +4278,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 25/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -4318,17 +4318,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 11º e 12º tempos</t>
+          <t>Terça, 29/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -4338,37 +4338,37 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 10º tempo</t>
+          <t>Segunda, 05/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 11º e 12º tempos</t>
+          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -4378,117 +4378,117 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Terça, 20/10/2026 — 11º ao 13º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 28/10/2026 — 10º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º tempo</t>
+          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 1º ao 3º tempos</t>
+          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 11/11/2026 — 6º tempo</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 12/11/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 9º e 10º tempos</t>
+          <t>Terça, 25/08/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -557,7 +557,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 19/08/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 26/08/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -577,7 +577,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -597,7 +597,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 03/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -617,7 +617,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 09/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -637,7 +637,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 11/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -677,7 +677,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 18/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -697,7 +697,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 21/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -707,117 +707,117 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 3º tempo</t>
+          <t>Quinta, 01/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 2º tempo</t>
+          <t>Sexta, 23/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 26/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -827,17 +827,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 03/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -847,37 +847,37 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 2º tempo</t>
+          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 11/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -887,41 +887,41 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 16/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 19/11/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 18/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -990,7 +990,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 9º e 10º tempos</t>
+          <t>Terça, 25/08/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 19/08/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 26/08/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 03/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 09/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 11/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 18/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 21/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -1160,117 +1160,117 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 3º tempo</t>
+          <t>Quinta, 01/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 2º tempo</t>
+          <t>Sexta, 23/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 26/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -1280,17 +1280,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 03/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -1300,37 +1300,37 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 2º tempo</t>
+          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 11/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -1340,41 +1340,41 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 16/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 19/11/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 18/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1433,17 +1433,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 10º e 11º tempos</t>
+          <t>Segunda, 24/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -1453,17 +1453,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 19/08/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 26/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1473,17 +1473,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 21/08/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -1493,37 +1493,37 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 1º ao 3º tempos</t>
+          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -1533,17 +1533,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1553,17 +1553,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1573,17 +1573,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -1593,37 +1593,37 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 17/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 2º ao 7º tempos</t>
+          <t>Sexta, 18/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -1653,37 +1653,37 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 1º tempo</t>
+          <t>Quinta, 24/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Terça, 22/09/2026 — 10º e 11º tempos</t>
+          <t>Sexta, 25/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -1693,37 +1693,37 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 5º tempo</t>
+          <t>Quarta, 30/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 01/10/2026 — 9º e 10º tempos</t>
+          <t>Quinta, 01/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -1733,17 +1733,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 06/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -1753,37 +1753,37 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 09/10/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -1793,37 +1793,37 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 21/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1833,17 +1833,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 12/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -1946,17 +1946,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 10º e 11º tempos</t>
+          <t>Segunda, 24/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -1966,17 +1966,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 19/08/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 26/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1986,17 +1986,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 21/08/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -2006,37 +2006,37 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 1º ao 3º tempos</t>
+          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 6º e 7º tempos</t>
+          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -2046,17 +2046,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -2066,17 +2066,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2086,17 +2086,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -2106,17 +2106,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -2126,21 +2126,21 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 2º ao 7º tempos</t>
+          <t>Sexta, 18/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -2166,37 +2166,37 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 1º tempo</t>
+          <t>Quinta, 24/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Terça, 22/09/2026 — 10º e 11º tempos</t>
+          <t>Sexta, 25/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -2206,37 +2206,37 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 5º tempo</t>
+          <t>Quarta, 30/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 01/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -2246,17 +2246,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 01/10/2026 — 9º e 10º tempos</t>
+          <t>Terça, 06/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -2266,37 +2266,37 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 09/10/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -2306,37 +2306,37 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 21/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -2346,12 +2346,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2366,41 +2366,41 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 09/11/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 1º ao 3º tempos</t>
+          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 24/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -2479,21 +2479,21 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>S3-11</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 19/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 25/08 e Quarta, 26/08/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 20/08/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -2519,17 +2519,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 1º e 2º tempos</t>
+          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -2539,21 +2539,21 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>S3-11</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08 e Quarta, 26/08/2026 — 2º ao 7º tempos</t>
+          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -2579,17 +2579,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2599,17 +2599,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 11º e 12º tempos</t>
+          <t>Quarta, 09/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -2619,17 +2619,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 1º e 2º tempos</t>
+          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 9º ao 11º tempos</t>
+          <t>Quinta, 17/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -2679,57 +2679,57 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 21/09/2026 — 4º ao 6º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 25/09/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 24/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 01/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -2739,17 +2739,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 05/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -2759,17 +2759,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 3º e 4º tempos</t>
+          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -2779,57 +2779,57 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>S4-11</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 3º ao 5º tempos</t>
+          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 9º tempo</t>
+          <t>Quarta, 28/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 6º e 7º tempos</t>
+          <t>Terça, 03/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -2839,17 +2839,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 05/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -2859,37 +2859,37 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>S4-11</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
+          <t>Terça, 10/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 4º tempo</t>
+          <t>Quarta, 11/11/2026 — 9º tempo</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -2899,17 +2899,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 8º e 9º tempos</t>
+          <t>Segunda, 16/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -2919,17 +2919,17 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 16/11/2026 — 2º e 3º tempos</t>
+          <t>Terça, 17/11/2026 — 8º e 9º tempos</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 24/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -3012,37 +3012,37 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>S3-11</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 19/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 25/08 e Quarta, 26/08/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 28/08/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -3052,37 +3052,37 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>S3-11</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 25/08 e Quarta, 26/08/2026 — 2º ao 7º tempos</t>
+          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -3092,17 +3092,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -3112,17 +3112,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 11º e 12º tempos</t>
+          <t>Terça, 08/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -3132,17 +3132,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 09/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -3152,17 +3152,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -3172,97 +3172,97 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 9º ao 11º tempos</t>
+          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 17/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 21/09/2026 — 4º ao 6º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 25/09/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 24/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 01/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -3272,17 +3272,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 3º e 4º tempos</t>
+          <t>Segunda, 05/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -3292,57 +3292,57 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 3º ao 5º tempos</t>
+          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>S4-11</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 9º tempo</t>
+          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 28/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -3352,17 +3352,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 03/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -3372,77 +3372,77 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>S4-11</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
+          <t>Quinta, 05/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 4º tempo</t>
+          <t>Terça, 10/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 11/11/2026 — 9º tempo</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 8º e 9º tempos</t>
+          <t>Segunda, 16/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -3452,17 +3452,17 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 16/11/2026 — 2º e 3º tempos</t>
+          <t>Terça, 17/11/2026 — 8º e 9º tempos</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
@@ -3525,57 +3525,57 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 1º ao 3º tempos</t>
+          <t>Segunda, 24/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 20/08/2026 — 9º e 10º tempos</t>
+          <t>Terça, 25/08/2026 — 10º ao 12º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -3585,17 +3585,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 10º e 11º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -3605,17 +3605,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -3625,17 +3625,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -3645,17 +3645,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 10/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -3665,17 +3665,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 11/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 15/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -3705,57 +3705,57 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>S4-12</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 16/09 e Quinta, 17/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>S4-12</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 16/09 e Quinta, 17/09/2026 — 2º ao 7º tempos</t>
+          <t>Sexta, 18/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 24/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 23/09/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -3765,17 +3765,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 25/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -3785,17 +3785,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 28/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -3805,17 +3805,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 29/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 11º ao 13º tempos</t>
+          <t>Terça, 20/10/2026 — 10º ao 12º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -3865,57 +3865,57 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 10º tempo</t>
+          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
+          <t>Terça, 03/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -3925,57 +3925,57 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 04/11/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 6º tempo</t>
+          <t>Segunda, 09/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 11/11/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -4038,57 +4038,57 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 18/08/2026 — 1º ao 3º tempos</t>
+          <t>Segunda, 24/08/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 20/08/2026 — 9º e 10º tempos</t>
+          <t>Terça, 25/08/2026 — 10º ao 12º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -4098,17 +4098,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 10º e 11º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -4118,17 +4118,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -4138,17 +4138,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -4158,17 +4158,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 10/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -4178,17 +4178,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 11/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 15/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -4218,57 +4218,57 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>S4-12</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 16/09 e Quinta, 17/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>S4-12</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 16/09 e Quinta, 17/09/2026 — 2º ao 7º tempos</t>
+          <t>Sexta, 18/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 24/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 23/09/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -4278,17 +4278,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 25/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -4298,17 +4298,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 29/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -4318,17 +4318,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 05/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -4338,17 +4338,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -4358,77 +4358,77 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Terça, 20/10/2026 — 10º ao 12º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 11º ao 13º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 10º tempo</t>
+          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
+          <t>Terça, 03/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -4438,57 +4438,57 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 04/11/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 6º tempo</t>
+          <t>Segunda, 09/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 11/11/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -1533,17 +1533,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1553,17 +1553,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1573,41 +1573,41 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
+          <t>Terça, 15/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1633,57 +1633,57 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>AG10</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 18/09/2026 — 2º ao 7º tempos</t>
+          <t>Segunda, 21/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>AG10</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 24/09/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 29/09/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -1693,17 +1693,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -1713,17 +1713,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 01/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -1733,17 +1733,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -1753,37 +1753,37 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 5º tempo</t>
+          <t>Quinta, 22/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
+          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -1793,17 +1793,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 1º tempo</t>
+          <t>Sexta, 30/10/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -1813,17 +1813,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1833,12 +1833,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1853,41 +1853,41 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 1º ao 3º tempos</t>
+          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 11/11/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2066,17 +2066,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2086,17 +2086,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -2106,97 +2106,97 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
+          <t>Terça, 15/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>AG10</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 18/09/2026 — 2º ao 7º tempos</t>
+          <t>Segunda, 21/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>AG10</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 24/09/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 29/09/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -2206,17 +2206,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -2226,17 +2226,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 01/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -2246,17 +2246,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 10º e 11º tempos</t>
+          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -2266,37 +2266,37 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 5º tempo</t>
+          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
+          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -2306,17 +2306,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 1º tempo</t>
+          <t>Sexta, 30/10/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -2326,17 +2326,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -2346,12 +2346,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2366,41 +2366,41 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 1º ao 3º tempos</t>
+          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 11/11/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -527,17 +527,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 9º e 10º tempos</t>
+          <t>Segunda, 24/08/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -547,17 +547,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 26/08/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 26/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -567,17 +567,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 02/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -587,17 +587,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 03/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -607,12 +607,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -627,17 +627,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -647,17 +647,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -687,17 +687,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 23/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -747,17 +747,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 07/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -767,17 +767,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -787,37 +787,37 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 1º tempo</t>
+          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 03/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -827,57 +827,57 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 04/11/2026 — 3º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 09/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 13/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -887,21 +887,21 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 16/11/2026 — 2º tempo</t>
+          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -980,17 +980,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 9º e 10º tempos</t>
+          <t>Segunda, 24/08/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -1000,17 +1000,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 26/08/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 26/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1020,17 +1020,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 02/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -1040,17 +1040,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 03/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -1060,12 +1060,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1080,17 +1080,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1100,17 +1100,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1140,17 +1140,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 23/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -1200,17 +1200,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 07/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -1220,17 +1220,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -1240,37 +1240,37 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 1º tempo</t>
+          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 03/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -1280,57 +1280,57 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 04/11/2026 — 3º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 09/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 13/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -1340,21 +1340,21 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 16/11/2026 — 2º tempo</t>
+          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 24/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 27/08/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -1633,57 +1633,57 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>AG10</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 1º ao 3º tempos</t>
+          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>AG10</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
+          <t>Terça, 29/09/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 10º e 11º tempos</t>
+          <t>Segunda, 05/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -1713,17 +1713,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -1733,17 +1733,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -1753,17 +1753,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 27/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -1773,17 +1773,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 29/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -1793,37 +1793,37 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 5º tempo</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
+          <t>Quinta, 05/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1833,41 +1833,41 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 06/11/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 09/11/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 24/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 27/08/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -2146,57 +2146,57 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>AG10</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 1º ao 3º tempos</t>
+          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>AG10</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
+          <t>Terça, 29/09/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 30/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -2206,17 +2206,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 05/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -2226,17 +2226,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -2246,17 +2246,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -2266,17 +2266,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -2286,17 +2286,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 27/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -2306,37 +2306,37 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 5º tempo</t>
+          <t>Quinta, 29/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -2346,41 +2346,41 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 06/11/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 09/11/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -2679,61 +2679,61 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 4º ao 6º tempos</t>
+          <t>Sexta, 25/09/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 4º tempo</t>
+          <t>Terça, 29/09/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 01/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 30/09/2026 — 9º tempo</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2759,77 +2759,77 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 19/10/2026 — 4º ao 6º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>S4-11</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
+          <t>Quinta, 22/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>S4-11</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 29/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -2839,17 +2839,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 2º e 3º tempos</t>
+          <t>Terça, 03/11/2026 — 8º e 9º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -2859,17 +2859,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -2879,37 +2879,37 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 9º tempo</t>
+          <t>Quarta, 11/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 16/11/2026 — 6º e 7º tempos</t>
+          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -2919,17 +2919,17 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 8º e 9º tempos</t>
+          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
@@ -3212,21 +3212,21 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 4º ao 6º tempos</t>
+          <t>Segunda, 21/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -3252,17 +3252,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 01/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 29/09/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -3272,37 +3272,37 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 30/09/2026 — 9º tempo</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 05/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -3312,37 +3312,37 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>S4-11</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
+          <t>Segunda, 19/10/2026 — 4º ao 6º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 22/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -3352,37 +3352,37 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>S4-11</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 2º e 3º tempos</t>
+          <t>Terça, 03/11/2026 — 8º e 9º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -3392,17 +3392,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -3412,37 +3412,37 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 9º tempo</t>
+          <t>Quarta, 11/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 16/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -3452,17 +3452,17 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 8º e 9º tempos</t>
+          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
@@ -3745,17 +3745,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 11º e 12º tempos</t>
+          <t>Segunda, 21/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -3765,37 +3765,37 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 23/09/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 02/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -3805,17 +3805,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 05/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -3825,77 +3825,77 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Terça, 06/10/2026 — 11º ao 13º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 10º ao 12º tempos</t>
+          <t>Terça, 20/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º tempo</t>
+          <t>Quarta, 21/10/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 29/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -3905,17 +3905,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 1º e 2º tempos</t>
+          <t>Terça, 03/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -3925,17 +3925,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º tempo</t>
+          <t>Quarta, 04/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -3945,17 +3945,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 11/11/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -3965,17 +3965,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 11º e 12º tempos</t>
+          <t>Quinta, 12/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -4038,41 +4038,41 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 6º e 7º tempos</t>
+          <t>Terça, 25/08/2026 — 10º ao 12º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 10º ao 12º tempos</t>
+          <t>Quinta, 27/08/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -4258,21 +4258,21 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 11º e 12º tempos</t>
+          <t>Quarta, 23/09/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 02/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -4298,17 +4298,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 05/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -4318,37 +4318,37 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 06/10/2026 — 11º ao 13º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Terça, 20/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -4358,57 +4358,57 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 10º ao 12º tempos</t>
+          <t>Quarta, 21/10/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º tempo</t>
+          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 29/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -4418,17 +4418,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 1º e 2º tempos</t>
+          <t>Terça, 03/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -4438,17 +4438,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º tempo</t>
+          <t>Quarta, 04/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -4458,17 +4458,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 11/11/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -4478,17 +4478,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 11º e 12º tempos</t>
+          <t>Quinta, 12/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -527,17 +527,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 6º e 7º tempos</t>
+          <t>Terça, 25/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -567,17 +567,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 28/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -587,17 +587,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -617,7 +617,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 08/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -627,17 +627,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -647,17 +647,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -667,17 +667,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 18/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -707,17 +707,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 01/10/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 25/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -727,77 +727,77 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Quarta, 30/09/2026 — 3º tempo</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 07/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -807,17 +807,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -827,57 +827,57 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 3º tempo</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 2º tempo</t>
+          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 13/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 12/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -887,41 +887,41 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 16/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 18/11/2026 — 2º tempo</t>
+          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -980,17 +980,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 6º e 7º tempos</t>
+          <t>Terça, 25/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -1020,17 +1020,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 28/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -1040,17 +1040,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 08/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -1080,17 +1080,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1100,17 +1100,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1120,17 +1120,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 18/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -1160,17 +1160,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 01/10/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 25/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -1180,77 +1180,77 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Quarta, 30/09/2026 — 3º tempo</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 07/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -1260,17 +1260,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -1280,57 +1280,57 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 3º tempo</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 2º tempo</t>
+          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 13/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 12/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -1340,41 +1340,41 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 16/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 18/11/2026 — 2º tempo</t>
+          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1433,37 +1433,37 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 24/08/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 26/08/2026 — 2º e 3º tempos</t>
+          <t>Terça, 25/08/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1473,17 +1473,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 26/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -1493,17 +1493,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 02/09/2026 — 3º e 4º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -1513,17 +1513,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -1553,17 +1553,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1573,37 +1573,37 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
+          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 14/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -1613,17 +1613,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -1653,57 +1653,57 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 10º e 11º tempos</t>
+          <t>Segunda, 28/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 02/10/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -1713,17 +1713,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -1733,17 +1733,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 19/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -1753,17 +1753,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Terça, 27/10/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -1773,17 +1773,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 9º e 10º tempos</t>
+          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -1793,37 +1793,37 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 28/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1833,61 +1833,61 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 5º tempo</t>
+          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 1º ao 3º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 1º tempo</t>
+          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1946,37 +1946,37 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 24/08/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 26/08/2026 — 2º e 3º tempos</t>
+          <t>Terça, 25/08/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1986,17 +1986,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 26/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -2006,17 +2006,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -2026,17 +2026,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -2046,17 +2046,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -2066,17 +2066,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2106,37 +2106,37 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
+          <t>Segunda, 14/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -2166,57 +2166,57 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 10º e 11º tempos</t>
+          <t>Segunda, 28/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 02/10/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -2286,37 +2286,37 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Terça, 27/10/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 28/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 9º e 10º tempos</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -2326,17 +2326,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
+          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -2346,61 +2346,61 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 5º tempo</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 1º ao 3º tempos</t>
+          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 1º tempo</t>
+          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2459,17 +2459,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 24/08/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -2499,17 +2499,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 27/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -2519,17 +2519,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -2539,17 +2539,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 01/09/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -2559,37 +2559,37 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2599,17 +2599,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -2639,17 +2639,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -2659,37 +2659,37 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 9º ao 11º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 4º tempo</t>
+          <t>Quarta, 23/09/2026 — 9º tempo</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -2699,17 +2699,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 10º e 11º tempos</t>
+          <t>Segunda, 28/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -2719,21 +2719,21 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 9º tempo</t>
+          <t>Terça, 29/09/2026 — 8º ao 10º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -2759,41 +2759,41 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 4º ao 6º tempos</t>
+          <t>Terça, 20/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 23/10/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2819,17 +2819,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -2839,17 +2839,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 8º e 9º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -2859,17 +2859,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 10/11/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -2879,17 +2879,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -2899,17 +2899,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 17/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -2992,57 +2992,57 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>S3-11</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 2º e 3º tempos</t>
+          <t>Terça, 25/08 e Quarta, 26/08/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>S3-11</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 25/08 e Quarta, 26/08/2026 — 2º ao 7º tempos</t>
+          <t>Quinta, 27/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 01/09/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -3072,37 +3072,37 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -3132,17 +3132,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 11/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -3172,17 +3172,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -3192,77 +3192,77 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 9º ao 11º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 23/09/2026 — 9º tempo</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 4º tempo</t>
+          <t>Terça, 29/09/2026 — 8º ao 10º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 10º e 11º tempos</t>
+          <t>Segunda, 05/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -3272,37 +3272,37 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 9º tempo</t>
+          <t>Segunda, 19/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 6º e 7º tempos</t>
+          <t>Terça, 20/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -3312,77 +3312,77 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 4º ao 6º tempos</t>
+          <t>Sexta, 23/10/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>S4-11</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>S4-11</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 8º e 9º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -3392,17 +3392,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 10/11/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -3412,17 +3412,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -3432,17 +3432,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 17/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -3525,52 +3525,52 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 1º e 2º tempos</t>
+          <t>Terça, 25/08/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 10º ao 12º tempos</t>
+          <t>Quinta, 27/08/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -3585,17 +3585,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -3605,17 +3605,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 03/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -3625,17 +3625,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -3645,17 +3645,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 9º e 10º tempos</t>
+          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -3665,17 +3665,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -3685,17 +3685,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 14/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -3705,97 +3705,97 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>S4-12</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 16/09 e Quinta, 17/09/2026 — 2º ao 7º tempos</t>
+          <t>Terça, 15/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>S4-12</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 18/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 16/09 e Quinta, 17/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 23/09/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 4º tempo</t>
+          <t>Sexta, 02/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 6º e 7º tempos</t>
+          <t>Terça, 06/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -3805,17 +3805,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -3825,37 +3825,37 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 11º ao 13º tempos</t>
+          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -3865,17 +3865,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 11º e 12º tempos</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -3885,7 +3885,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -3905,17 +3905,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -3925,37 +3925,37 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º tempo</t>
+          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 11º e 12º tempos</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -3965,21 +3965,21 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 11/11/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4038,47 +4038,47 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 10º ao 12º tempos</t>
+          <t>Segunda, 24/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 11º e 12º tempos</t>
+          <t>Terça, 25/08/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 27/08/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -4098,17 +4098,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -4118,17 +4118,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -4138,17 +4138,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -4158,17 +4158,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 9º e 10º tempos</t>
+          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -4178,17 +4178,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -4198,17 +4198,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 14/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -4218,57 +4218,57 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>S4-12</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 16/09 e Quinta, 17/09/2026 — 2º ao 7º tempos</t>
+          <t>Terça, 15/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>S4-12</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 18/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 16/09 e Quinta, 17/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 4º tempo</t>
+          <t>Quarta, 23/09/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -4278,17 +4278,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 28/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -4298,57 +4298,57 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 02/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 11º ao 13º tempos</t>
+          <t>Terça, 06/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 11º e 12º tempos</t>
+          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -4378,17 +4378,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -4398,17 +4398,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 9º e 10º tempos</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -4418,17 +4418,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -4438,37 +4438,37 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º tempo</t>
+          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 11º e 12º tempos</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -4478,21 +4478,21 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 11/11/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -547,17 +547,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 26/08/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 28/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -567,17 +567,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -1000,17 +1000,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 26/08/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 28/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1020,17 +1020,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -1433,21 +1433,21 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 1º ao 3º tempos</t>
+          <t>Segunda, 24/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1593,21 +1593,21 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1946,21 +1946,21 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 1º ao 3º tempos</t>
+          <t>Segunda, 24/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2106,21 +2106,21 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -2499,17 +2499,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -2519,17 +2519,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
+          <t>Terça, 01/09/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -2539,57 +2539,57 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 11º e 12º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
+          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2599,17 +2599,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -2619,17 +2619,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -2639,17 +2639,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -2659,17 +2659,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 21/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -3012,17 +3012,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -3032,17 +3032,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
+          <t>Terça, 01/09/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -3052,57 +3052,57 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 11º e 12º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
+          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -3112,17 +3112,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 11/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -3132,17 +3132,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -3152,17 +3152,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -3172,17 +3172,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -3192,17 +3192,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 21/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -3525,37 +3525,37 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 9º ao 11º tempos</t>
+          <t>Terça, 25/08/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 9º e 10º tempos</t>
+          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -3585,21 +3585,21 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 01/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3705,17 +3705,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 1º e 2º tempos</t>
+          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -3765,57 +3765,57 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 1º ao 3º tempos</t>
+          <t>Quarta, 30/09/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 02/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Terça, 06/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -3825,17 +3825,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
+          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -3845,17 +3845,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -3865,17 +3865,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -3885,17 +3885,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -3905,17 +3905,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -3925,17 +3925,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -3945,17 +3945,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -3965,21 +3965,21 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 4º tempo</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4058,37 +4058,37 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 9º ao 11º tempos</t>
+          <t>Terça, 25/08/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 9º e 10º tempos</t>
+          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -4118,21 +4118,21 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 01/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -4218,17 +4218,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 1º e 2º tempos</t>
+          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -4298,57 +4298,57 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 1º ao 3º tempos</t>
+          <t>Quarta, 30/09/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 02/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Terça, 06/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -4358,17 +4358,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
+          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -4378,17 +4378,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -4398,17 +4398,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -4418,17 +4418,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -4438,17 +4438,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -4458,17 +4458,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -4478,21 +4478,21 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 4º tempo</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -687,17 +687,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 25/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -707,97 +707,97 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 30/09/2026 — 3º tempo</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 3º tempo</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Quarta, 07/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 2º tempo</t>
+          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -887,41 +887,41 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 16/11/2026 — 2º tempo</t>
+          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 23/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1140,17 +1140,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 25/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -1160,97 +1160,97 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 30/09/2026 — 3º tempo</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 3º tempo</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Quarta, 07/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 2º tempo</t>
+          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -1340,41 +1340,41 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 16/11/2026 — 2º tempo</t>
+          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 23/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1493,37 +1493,37 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 3º e 4º tempos</t>
+          <t>Segunda, 31/08/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 02/09/2026 — 3º e 4º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -1533,17 +1533,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1553,17 +1553,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1573,17 +1573,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -1593,21 +1593,21 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
+          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -2006,37 +2006,37 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 31/08/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º e 10º tempos</t>
+          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -2046,17 +2046,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -2066,17 +2066,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2086,17 +2086,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -2106,21 +2106,21 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 1º ao 3º tempos</t>
+          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -2899,17 +2899,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -2919,17 +2919,17 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 24/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
@@ -3432,17 +3432,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -3452,17 +3452,17 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 24/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
@@ -3805,17 +3805,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -3825,17 +3825,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -3845,17 +3845,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
+          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -3865,17 +3865,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -3885,17 +3885,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -3905,17 +3905,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
+          <t>Terça, 03/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -4338,17 +4338,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -4358,17 +4358,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -4378,17 +4378,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
+          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -4398,17 +4398,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -4418,17 +4418,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -4438,17 +4438,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
+          <t>Terça, 03/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -707,77 +707,77 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 3º tempo</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 2º tempo</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -787,37 +787,37 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 26/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -827,21 +827,21 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 30/10/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -867,37 +867,37 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 05/11/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 12/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -907,21 +907,21 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 23/11/2026 — 2º tempo</t>
+          <t>Segunda, 23/11/2026 — 3º e 4º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1160,77 +1160,77 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 3º tempo</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 2º tempo</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -1240,37 +1240,37 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 26/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -1280,21 +1280,21 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 30/10/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1320,37 +1320,37 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 05/11/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 12/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -1360,21 +1360,21 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 23/11/2026 — 2º tempo</t>
+          <t>Segunda, 23/11/2026 — 3º e 4º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1533,17 +1533,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1553,17 +1553,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1573,17 +1573,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -1593,17 +1593,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 17/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -1613,97 +1613,97 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>AG10</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>AG10</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
+          <t>Sexta, 02/10/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 1º ao 3º tempos</t>
+          <t>Quinta, 08/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 5º tempo</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Segunda, 19/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -1713,17 +1713,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -1733,17 +1733,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 22/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -1753,77 +1753,77 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 26/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 28/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 1º tempo</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1833,17 +1833,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -1853,17 +1853,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -1873,17 +1873,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 12/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -2046,17 +2046,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -2066,17 +2066,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2086,17 +2086,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -2106,17 +2106,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 17/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -2126,97 +2126,97 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>AG10</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>AG10</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
+          <t>Sexta, 02/10/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 1º ao 3º tempos</t>
+          <t>Quinta, 08/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 5º tempo</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -2226,17 +2226,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 22/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -2246,77 +2246,77 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 26/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 28/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 1º tempo</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -2326,17 +2326,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -2346,17 +2346,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -2366,17 +2366,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -2386,17 +2386,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 12/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -3745,17 +3745,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 2º tempo</t>
+          <t>Quarta, 30/09/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -3765,41 +3765,41 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 4º tempo</t>
+          <t>Sexta, 02/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 1º ao 3º tempos</t>
+          <t>Quarta, 07/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -4258,81 +4258,81 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 2º tempo</t>
+          <t>Segunda, 28/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 30/09/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 4º tempo</t>
+          <t>Sexta, 02/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 1º ao 3º tempos</t>
+          <t>Quarta, 07/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -917,7 +917,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 23/11/2026 — 3º e 4º tempos</t>
+          <t>Segunda, 23/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 23/11/2026 — 3º e 4º tempos</t>
+          <t>Segunda, 23/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 9º e 10º tempos</t>
+          <t>Terça, 25/08/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 27/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 9º e 10º tempos</t>
+          <t>Terça, 25/08/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 27/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -727,17 +727,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -747,17 +747,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -767,17 +767,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -787,97 +787,97 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 1º tempo</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 30/10/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 7º tempo</t>
+          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 05/11/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 7º tempo</t>
+          <t>Terça, 10/11/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -917,7 +917,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 23/11/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 16/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1180,17 +1180,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -1200,17 +1200,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -1220,17 +1220,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -1240,97 +1240,97 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 1º tempo</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 30/10/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 7º tempo</t>
+          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 05/11/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 7º tempo</t>
+          <t>Terça, 10/11/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 23/11/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 16/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 10/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -2206,17 +2206,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -2226,17 +2226,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -2246,77 +2246,77 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 1º ao 3º tempos</t>
+          <t>Quinta, 22/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 1º tempo</t>
+          <t>Segunda, 26/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 28/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -2326,17 +2326,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
+          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -2346,17 +2346,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -2366,17 +2366,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 10/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -2719,37 +2719,37 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 8º ao 10º tempos</t>
+          <t>Segunda, 05/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 6º e 7º tempos</t>
+          <t>Terça, 20/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -2759,97 +2759,97 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 23/10/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>S4-11</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 4º tempo</t>
+          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>S4-11</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 05/11/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
+          <t>Terça, 10/11/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -2859,17 +2859,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -2879,17 +2879,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 18/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -3232,37 +3232,37 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Terça, 29/09/2026 — 8º ao 10º tempos</t>
+          <t>Segunda, 05/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 19/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -3272,17 +3272,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 20/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -3292,97 +3292,97 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 23/10/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>S4-11</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 4º tempo</t>
+          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>S4-11</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 05/11/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
+          <t>Terça, 10/11/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -3392,17 +3392,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -3412,17 +3412,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 18/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -3525,21 +3525,21 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 5º e 6º tempos</t>
+          <t>Terça, 25/08/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -3585,21 +3585,21 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 9º ao 11º tempos</t>
+          <t>Terça, 01/09/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3745,97 +3745,97 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 4º tempo</t>
+          <t>Sexta, 02/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 1º ao 3º tempos</t>
+          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 2º tempo</t>
+          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 21/10/2026 — 10º tempo</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
+          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -3845,21 +3845,21 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 28/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -4058,21 +4058,21 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 5º e 6º tempos</t>
+          <t>Terça, 25/08/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -4118,21 +4118,21 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 9º ao 11º tempos</t>
+          <t>Terça, 01/09/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -4278,97 +4278,97 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 30/09/2026 — 4º tempo</t>
+          <t>Sexta, 02/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 1º ao 3º tempos</t>
+          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 2º tempo</t>
+          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 21/10/2026 — 10º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
+          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -4378,21 +4378,21 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 28/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -3735,7 +3735,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 16/09 e Quinta, 17/09/2026 — 2º ao 7º tempos</t>
+          <t>Quarta, 23/09 e Quinta, 24/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 16/09 e Quinta, 17/09/2026 — 2º ao 7º tempos</t>
+          <t>Quarta, 23/09 e Quinta, 24/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -3745,41 +3745,41 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 1º ao 3º tempos</t>
+          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -4278,41 +4278,41 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 1º ao 3º tempos</t>
+          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Quinta, 01/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -4258,17 +4258,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 01/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -4278,17 +4278,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 9º e 10º tempos</t>
+          <t>Segunda, 05/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -2499,17 +2499,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 02/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -2519,57 +2519,57 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 11º e 12º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
+          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -2579,17 +2579,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2599,17 +2599,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -2619,17 +2619,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -2639,17 +2639,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 21/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -2659,57 +2659,57 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 23/09/2026 — 9º tempo</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 9º tempo</t>
+          <t>Segunda, 28/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 07/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -2719,17 +2719,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 21/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -2739,117 +2739,117 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 23/10/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>S4-11</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 4º tempo</t>
+          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>S4-11</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 05/11/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 9º ao 11º tempos</t>
+          <t>Terça, 10/11/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -2859,17 +2859,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 16/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -3012,17 +3012,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 02/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -3032,57 +3032,57 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 11º e 12º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
+          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -3092,17 +3092,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 11/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -3112,17 +3112,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -3132,17 +3132,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -3152,17 +3152,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -3172,17 +3172,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 21/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -3192,57 +3192,57 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 23/09/2026 — 9º tempo</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 9º tempo</t>
+          <t>Quarta, 07/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 19/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -3252,17 +3252,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 21/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -3272,117 +3272,117 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 23/10/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>S4-11</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 4º tempo</t>
+          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>S4-11</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 05/11/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 9º ao 11º tempos</t>
+          <t>Terça, 10/11/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -3392,17 +3392,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 16/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -21,8 +21,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'9C2'!$A$2:$D$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'10C1'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'10C2'!$A$2:$D$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'11C1'!$A$2:$D$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'11C2'!$A$2:$D$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'11C1'!$A$2:$D$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'11C2'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'12C1'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'12C2'!$A$2:$D$25</definedName>
   </definedNames>
@@ -2418,7 +2418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2739,97 +2739,97 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>S4-11</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 4º tempo</t>
+          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>S4-11</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 05/11/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 9º ao 11º tempos</t>
+          <t>Terça, 10/11/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -2839,17 +2839,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 16/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -2859,17 +2859,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 16/11/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 18/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -2879,17 +2879,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 18/11/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -2899,45 +2899,25 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 24/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Qui</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Terça, 24/11/2026 — 1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:D26"/>
+  <autoFilter ref="A2:D25"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -2951,7 +2931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3272,97 +3252,97 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>S4-11</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 4º tempo</t>
+          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>S4-11</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 05/11/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 9º ao 11º tempos</t>
+          <t>Terça, 10/11/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -3372,17 +3352,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 16/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -3392,17 +3372,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 16/11/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 18/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -3412,17 +3392,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 18/11/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -3432,45 +3412,25 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 24/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Qui</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Terça, 24/11/2026 — 1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:D26"/>
+  <autoFilter ref="A2:D25"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -23,8 +23,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'10C2'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'11C1'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'11C2'!$A$2:$D$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'12C1'!$A$2:$D$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'12C2'!$A$2:$D$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'12C1'!$A$2:$D$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'12C2'!$A$2:$D$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3444,7 +3444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3885,17 +3885,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -3905,45 +3905,25 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Mat</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:D25"/>
+  <autoFilter ref="A2:D24"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -3957,7 +3937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4238,137 +4218,137 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
+          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 21/10/2026 — 10º tempo</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 10º tempo</t>
+          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 28/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 2º tempo</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -4378,17 +4358,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
+          <t>Terça, 03/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -4398,17 +4378,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -4418,45 +4398,25 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Mat</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:D25"/>
+  <autoFilter ref="A2:D24"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -3988,7 +3988,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 24/08/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -23,8 +23,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'10C2'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'11C1'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'11C2'!$A$2:$D$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'12C1'!$A$2:$D$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'12C2'!$A$2:$D$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'12C1'!$A$2:$D$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'12C2'!$A$2:$D$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3444,7 +3444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3885,17 +3885,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -3905,45 +3905,25 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Mat</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:D25"/>
+  <autoFilter ref="A2:D24"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -3957,7 +3937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4008,7 +3988,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 24/08/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -4238,137 +4218,137 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 05/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
+          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 21/10/2026 — 10º tempo</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 10º tempo</t>
+          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 28/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 2º tempo</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -4378,17 +4358,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
+          <t>Terça, 03/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -4398,17 +4378,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -4418,45 +4398,25 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Mat</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:D25"/>
+  <autoFilter ref="A2:D24"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -547,17 +547,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -567,17 +567,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -587,17 +587,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -607,17 +607,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -627,17 +627,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -647,17 +647,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -667,77 +667,77 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 18/09/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -747,17 +747,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -767,17 +767,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -787,77 +787,77 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 30/10/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 7º tempo</t>
+          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 05/11/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 7º tempo</t>
+          <t>Terça, 10/11/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -867,41 +867,41 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 1º tempo</t>
+          <t>Quinta, 12/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 13/11/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1000,17 +1000,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1020,17 +1020,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -1040,17 +1040,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -1060,17 +1060,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -1080,17 +1080,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1100,17 +1100,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1120,77 +1120,77 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 18/09/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -1200,17 +1200,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -1220,17 +1220,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -1240,77 +1240,77 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 30/10/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 7º tempo</t>
+          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 05/11/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 7º tempo</t>
+          <t>Terça, 10/11/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -1320,41 +1320,41 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 1º tempo</t>
+          <t>Quinta, 12/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 13/11/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -17,8 +17,8 @@
     <sheet name="12C2" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'9C1'!$A$2:$D$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'9C2'!$A$2:$D$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'9C1'!$A$2:$D$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'9C2'!$A$2:$D$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'10C1'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'10C2'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'11C1'!$A$2:$D$25</definedName>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -627,17 +627,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -647,77 +647,77 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 18/09/2026 — 5º tempo</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -727,17 +727,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 27/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -747,17 +747,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -767,165 +767,85 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 30/10/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 7º tempo</t>
+          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 05/11/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 7º tempo</t>
+          <t>Segunda, 16/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Bio</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Terça, 10/11/2026 — 1º tempo</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>DaF</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Quinta, 12/11/2026 — 1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Sexta, 13/11/2026 — 5º tempo</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Redação</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Segunda, 16/11/2026 — 6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D22"/>
+  <autoFilter ref="A2:D18"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -939,7 +859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1080,17 +1000,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1100,77 +1020,77 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 18/09/2026 — 5º tempo</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -1180,17 +1100,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 27/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -1200,17 +1120,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -1220,165 +1140,85 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 30/10/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 7º tempo</t>
+          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 05/11/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 7º tempo</t>
+          <t>Segunda, 16/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Bio</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Terça, 10/11/2026 — 1º tempo</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>DaF</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Quinta, 12/11/2026 — 1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Sexta, 13/11/2026 — 5º tempo</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Redação</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Segunda, 16/11/2026 — 6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D22"/>
+  <autoFilter ref="A2:D18"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -17,8 +17,8 @@
     <sheet name="12C2" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'9C1'!$A$2:$D$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'9C2'!$A$2:$D$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'9C1'!$A$2:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'9C2'!$A$2:$D$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'10C1'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'10C2'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'11C1'!$A$2:$D$25</definedName>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -547,17 +547,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -567,17 +567,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -587,17 +587,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -607,17 +607,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Terça, 08/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -627,17 +627,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -687,17 +687,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 19/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -827,25 +827,45 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 16/11/2026 — 6º e 7º tempos</t>
+          <t>Terça, 10/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
         <v>2</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Bio</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Terça, 17/11/2026 — 4º tempo</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:D18"/>
+  <autoFilter ref="A2:D19"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -859,7 +879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -920,17 +940,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -940,17 +960,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -960,17 +980,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -980,17 +1000,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Terça, 08/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -1000,17 +1020,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1060,17 +1080,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 19/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -1200,25 +1220,45 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 16/11/2026 — 6º e 7º tempos</t>
+          <t>Terça, 10/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
         <v>2</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Bio</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Terça, 17/11/2026 — 4º tempo</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:D18"/>
+  <autoFilter ref="A2:D19"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -17,8 +17,8 @@
     <sheet name="12C2" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'9C1'!$A$2:$D$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'9C2'!$A$2:$D$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'9C1'!$A$2:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'9C2'!$A$2:$D$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'10C1'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'10C2'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'11C1'!$A$2:$D$25</definedName>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -547,17 +547,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -567,17 +567,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -587,17 +587,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -607,17 +607,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Terça, 08/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -627,17 +627,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -647,77 +647,77 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 18/09/2026 — 5º tempo</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Segunda, 19/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -727,17 +727,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 27/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -747,17 +747,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -767,81 +767,81 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 30/10/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 7º tempo</t>
+          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 05/11/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 7º tempo</t>
+          <t>Terça, 10/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -857,75 +857,15 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 1º tempo</t>
+          <t>Terça, 17/11/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>DaF</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Quinta, 12/11/2026 — 1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Sexta, 13/11/2026 — 5º tempo</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Redação</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Segunda, 16/11/2026 — 6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:D22"/>
+  <autoFilter ref="A2:D19"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -939,7 +879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1000,17 +940,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1020,17 +960,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -1040,17 +980,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -1060,17 +1000,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Terça, 08/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -1080,17 +1020,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1100,77 +1040,77 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 18/09/2026 — 5º tempo</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Segunda, 19/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -1180,17 +1120,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 27/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -1200,17 +1140,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -1220,81 +1160,81 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 30/10/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 7º tempo</t>
+          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 05/11/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 7º tempo</t>
+          <t>Terça, 10/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1310,75 +1250,15 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 1º tempo</t>
+          <t>Terça, 17/11/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>DaF</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Quinta, 12/11/2026 — 1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Sexta, 13/11/2026 — 5º tempo</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Redação</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Segunda, 16/11/2026 — 6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:D22"/>
+  <autoFilter ref="A2:D19"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -687,17 +687,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -707,17 +707,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -1080,17 +1080,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -1100,17 +1100,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -17,14 +17,14 @@
     <sheet name="12C2" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'9C1'!$A$2:$D$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'9C2'!$A$2:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'9C1'!$A$2:$D$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'9C2'!$A$2:$D$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'10C1'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'10C2'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'11C1'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'11C2'!$A$2:$D$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'12C1'!$A$2:$D$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'12C2'!$A$2:$D$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'12C1'!$A$2:$D$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'12C2'!$A$2:$D$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -527,37 +527,37 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DSD1</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 19/08/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 25/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -567,17 +567,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -587,57 +587,57 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DSD1</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 31/08/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DSD1</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 9º e 10º tempos</t>
+          <t>Terça, 01/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -647,37 +647,37 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -687,17 +687,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -707,17 +707,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 15/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -727,37 +727,37 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Terça, 27/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -767,37 +767,37 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 5º tempo</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -807,37 +807,37 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 7º tempo</t>
+          <t>Terça, 27/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -847,25 +847,105 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 1º tempo</t>
+          <t>Quinta, 05/11/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Hist</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Terça, 10/11/2026 — 4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Sexta, 13/11/2026 — 5º tempo</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Bio</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Terça, 17/11/2026 — 1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Mat</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Quarta, 18/11/2026 — 4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:D19"/>
+  <autoFilter ref="A2:D23"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -879,7 +959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -920,37 +1000,37 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DSD1</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 19/08/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 25/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -960,17 +1040,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -980,57 +1060,57 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DSD1</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 31/08/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DSD1</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 9º e 10º tempos</t>
+          <t>Terça, 01/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1040,37 +1120,37 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -1080,17 +1160,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -1100,17 +1180,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 15/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -1120,37 +1200,37 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Terça, 27/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -1160,37 +1240,37 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 5º tempo</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -1200,37 +1280,37 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 7º tempo</t>
+          <t>Terça, 27/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -1240,25 +1320,105 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 1º tempo</t>
+          <t>Quinta, 05/11/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Hist</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Terça, 10/11/2026 — 4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Sexta, 13/11/2026 — 5º tempo</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Bio</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Terça, 17/11/2026 — 1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Mat</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Quarta, 18/11/2026 — 4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:D19"/>
+  <autoFilter ref="A2:D23"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -3324,7 +3484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3365,37 +3525,37 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DSD2</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 9º ao 11º tempos</t>
+          <t>Terça, 18/08/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 24/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -3405,37 +3565,37 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 25/08/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 5º e 6º tempos</t>
+          <t>Quinta, 27/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -3445,17 +3605,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -3465,17 +3625,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 11º e 12º tempos</t>
+          <t>Terça, 01/09/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -3485,37 +3645,37 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DSD2</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -3525,17 +3685,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -3545,17 +3705,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -3565,37 +3725,37 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>S4-12</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 23/09 e Quinta, 24/09/2026 — 2º ao 7º tempos</t>
+          <t>Segunda, 14/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 01/10/2026 — 9º e 10º tempos</t>
+          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -3605,37 +3765,37 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>S4-12</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
+          <t>Quarta, 23/09 e Quinta, 24/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
+          <t>Quinta, 01/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -3645,37 +3805,37 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 10º tempo</t>
+          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -3685,17 +3845,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 2º tempo</t>
+          <t>Quarta, 21/10/2026 — 10º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -3705,17 +3865,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -3725,37 +3885,37 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 28/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -3765,17 +3925,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -3785,25 +3945,65 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
+          <t>Bio</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Terça, 03/11/2026 — 1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Qui</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
           <t>Mat</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D26" s="8" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D24"/>
+  <autoFilter ref="A2:D26"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -3817,7 +4017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3858,77 +4058,77 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DSD2</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 5º e 6º tempos</t>
+          <t>Terça, 18/08/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 9º ao 11º tempos</t>
+          <t>Segunda, 24/08/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 2º e 3º tempos</t>
+          <t>Terça, 25/08/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 27/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -3938,17 +4138,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 5º e 6º tempos</t>
+          <t>Segunda, 31/08/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -3958,17 +4158,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 11º e 12º tempos</t>
+          <t>Terça, 01/09/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -3978,37 +4178,37 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DSD2</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 11º e 12º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -4018,17 +4218,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -4038,17 +4238,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -4058,37 +4258,37 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>S4-12</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 23/09 e Quinta, 24/09/2026 — 2º ao 7º tempos</t>
+          <t>Segunda, 14/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 01/10/2026 — 9º e 10º tempos</t>
+          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -4098,37 +4298,37 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>S4-12</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
+          <t>Quarta, 23/09 e Quinta, 24/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
+          <t>Quinta, 01/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -4138,37 +4338,37 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 10º tempo</t>
+          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -4178,17 +4378,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 2º tempo</t>
+          <t>Quarta, 21/10/2026 — 10º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -4198,17 +4398,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -4218,37 +4418,37 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 28/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -4258,17 +4458,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -4278,25 +4478,65 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
+          <t>Bio</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Terça, 03/11/2026 — 1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Qui</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
           <t>Mat</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D26" s="8" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D24"/>
+  <autoFilter ref="A2:D26"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -567,21 +567,21 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DSD1</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 31/08/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -597,7 +597,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 2º ao 7º tempos</t>
+          <t>Terça, 01/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -607,37 +607,37 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DSD1</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 2º ao 7º tempos</t>
+          <t>Quinta, 03/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -647,17 +647,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -667,17 +667,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -687,17 +687,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Terça, 15/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -707,17 +707,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -1040,21 +1040,21 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DSD1</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 31/08/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 2º ao 7º tempos</t>
+          <t>Terça, 01/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -1080,37 +1080,37 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DSD1</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 2º ao 7º tempos</t>
+          <t>Quinta, 03/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1120,17 +1120,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1140,17 +1140,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 9º e 10º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -1160,17 +1160,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Terça, 15/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -1180,17 +1180,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -3865,57 +3865,57 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 28/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 2º tempo</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -3925,17 +3925,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
+          <t>Terça, 03/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -3945,17 +3945,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -3965,17 +3965,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 09/11/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -4398,57 +4398,57 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 28/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 2º tempo</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -4458,17 +4458,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
+          <t>Terça, 03/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -4478,17 +4478,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -4498,17 +4498,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 09/11/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 3º e 4º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -1733,17 +1733,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -1753,17 +1753,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 22/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -1773,77 +1773,77 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 9º e 10º tempos</t>
+          <t>Segunda, 26/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 1º ao 3º tempos</t>
+          <t>Quarta, 28/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 1º tempo</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -1853,17 +1853,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1873,17 +1873,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 05/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 1º e 2º tempos</t>
+          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -2759,57 +2759,57 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>S4-11</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>S4-11</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Terça, 03/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 1º e 2º tempos</t>
+          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -3272,57 +3272,57 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>S4-11</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>S4-11</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10 e Terça, 27/10/2026 — 2º ao 7º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Terça, 03/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -747,17 +747,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -767,17 +767,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -787,17 +787,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 27/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -807,17 +807,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 27/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -827,57 +827,57 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 05/11/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 7º tempo</t>
+          <t>Sexta, 06/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -907,17 +907,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 1º e 2º tempos</t>
+          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1220,17 +1220,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -1240,17 +1240,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -1260,17 +1260,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 27/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -1280,17 +1280,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 27/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -1300,57 +1300,57 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 05/11/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 7º tempo</t>
+          <t>Sexta, 06/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -1380,17 +1380,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 1º e 2º tempos</t>
+          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -1673,37 +1673,37 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 5º tempo</t>
+          <t>Quinta, 08/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -1713,17 +1713,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -1733,17 +1733,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 22/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -1753,77 +1753,77 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 9º e 10º tempos</t>
+          <t>Segunda, 26/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 1º ao 3º tempos</t>
+          <t>Quarta, 28/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 1º tempo</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -1833,17 +1833,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -1853,17 +1853,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 05/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1873,17 +1873,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -1893,17 +1893,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 10/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -1913,21 +1913,21 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 11/11/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2186,37 +2186,37 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 5º tempo</t>
+          <t>Quinta, 08/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -2226,17 +2226,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -2246,17 +2246,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -2266,17 +2266,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 22/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -2286,77 +2286,77 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 9º e 10º tempos</t>
+          <t>Segunda, 26/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 1º ao 3º tempos</t>
+          <t>Quarta, 28/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 1º tempo</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -2366,17 +2366,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -2386,21 +2386,21 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 06/11/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -2316,7 +2316,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 1º tempo</t>
+          <t>Quarta, 28/10/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 9º tempo</t>
+          <t>Quarta, 23/09/2026 — 11º tempo</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 10º tempo</t>
+          <t>Quarta, 21/10/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 2º tempo</t>
+          <t>Quarta, 28/10/2026 — 6º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -3845,17 +3845,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 10º tempo</t>
+          <t>Quarta, 21/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -3925,37 +3925,37 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 04/11/2026 — 10º tempo</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 09/11/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -3965,17 +3965,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 5º e 6º tempos</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -3985,17 +3985,17 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 12/11/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
@@ -4378,17 +4378,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º tempo</t>
+          <t>Quarta, 21/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -4458,37 +4458,37 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 04/11/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 09/11/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -4498,17 +4498,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 5º e 6º tempos</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -4518,17 +4518,17 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 12/11/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -3865,37 +3865,37 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 2º tempo</t>
+          <t>Sexta, 23/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 26/10/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -3905,61 +3905,61 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 28/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 10º tempo</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 5º e 6º tempos</t>
+          <t>Quarta, 04/11/2026 — 10º tempo</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -4398,37 +4398,37 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º tempo</t>
+          <t>Sexta, 23/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 26/10/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -4438,61 +4438,61 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 30/10/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º tempo</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º tempo</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 5º e 6º tempos</t>
+          <t>Quarta, 04/11/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -17,8 +17,8 @@
     <sheet name="12C2" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'9C1'!$A$2:$D$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'9C2'!$A$2:$D$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'9C1'!$A$2:$D$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'9C2'!$A$2:$D$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'10C1'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'10C2'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'11C1'!$A$2:$D$25</definedName>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -827,17 +827,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 7º tempo</t>
+          <t>Quarta, 04/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -847,37 +847,37 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 05/11/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 06/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -887,65 +887,85 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 13/11/2026 — 5º tempo</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 13/11/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>Hist</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
           <t>Mat</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>Quarta, 18/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D24" s="8" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D23"/>
+  <autoFilter ref="A2:D24"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -959,7 +979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1300,17 +1320,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 7º tempo</t>
+          <t>Quarta, 04/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -1320,37 +1340,37 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 05/11/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 06/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -1360,65 +1380,85 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 13/11/2026 — 5º tempo</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 13/11/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>Hist</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
           <t>Mat</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>Quarta, 18/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D24" s="8" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D23"/>
+  <autoFilter ref="A2:D24"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -3885,37 +3885,37 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 1º tempo</t>
+          <t>Sexta, 23/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 26/10/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -3925,81 +3925,81 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 5º e 6º tempos</t>
+          <t>Quarta, 28/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 2º tempo</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 04/11/2026 — 10º tempo</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 10º tempo</t>
+          <t>Segunda, 09/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -4418,37 +4418,37 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 1º tempo</t>
+          <t>Sexta, 23/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 6º e 7º tempos</t>
+          <t>Segunda, 26/10/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -4458,81 +4458,81 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 5º e 6º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º tempo</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º tempo</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 04/11/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º tempo</t>
+          <t>Segunda, 09/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -2266,17 +2266,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -2286,17 +2286,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 22/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -2306,77 +2306,77 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 9º e 10º tempos</t>
+          <t>Segunda, 26/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 1º ao 3º tempos</t>
+          <t>Quarta, 28/10/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 7º tempo</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -2386,17 +2386,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -2406,57 +2406,57 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 06/11/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 5º tempo</t>
+          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 10/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -2466,17 +2466,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -1713,17 +1713,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 07/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -1733,17 +1733,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 08/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -1753,17 +1753,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -1773,77 +1773,77 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 9º e 10º tempos</t>
+          <t>Segunda, 19/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 1º ao 3º tempos</t>
+          <t>Quarta, 21/10/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 1º tempo</t>
+          <t>Quinta, 22/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -1853,37 +1853,37 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 28/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -1893,17 +1893,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 2º e 3º tempos</t>
+          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1913,17 +1913,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -1933,17 +1933,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 10º e 11º tempos</t>
+          <t>Quinta, 05/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -1953,21 +1953,21 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 11/11/2026 — 5º tempo</t>
+          <t>Terça, 10/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2226,17 +2226,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 07/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -2246,17 +2246,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 08/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -2266,17 +2266,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -2286,57 +2286,57 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 9º e 10º tempos</t>
+          <t>Segunda, 19/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 1º ao 3º tempos</t>
+          <t>Quinta, 22/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 7º tempo</t>
+          <t>Sexta, 23/10/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -2346,17 +2346,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -2366,37 +2366,37 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 28/10/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -2406,37 +2406,37 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 5º tempo</t>
+          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -3885,17 +3885,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 22/10/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -3905,17 +3905,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 5º e 6º tempos</t>
+          <t>Sexta, 23/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -3925,97 +3925,97 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 2º tempo</t>
+          <t>Segunda, 26/10/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 28/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 10º tempo</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 04/11/2026 — 10º tempo</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 09/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -4025,17 +4025,17 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 5º e 6º tempos</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
@@ -4418,17 +4418,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 22/10/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -4438,17 +4438,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 5º e 6º tempos</t>
+          <t>Sexta, 23/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -4458,97 +4458,97 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º tempo</t>
+          <t>Segunda, 26/10/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º tempo</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º tempo</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 09/11/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 04/11/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 09/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -4558,17 +4558,17 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 12/11/2026 — 5º e 6º tempos</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -1513,17 +1513,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 25/08/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -1533,17 +1533,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 26/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -1553,17 +1553,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 26/08/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 28/08/2026 — 3º e 4º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -2026,17 +2026,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 24/08/2026 — 4º e 5º tempos</t>
+          <t>Terça, 25/08/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -2046,17 +2046,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 25/08/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 26/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -2066,17 +2066,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 26/08/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 28/08/2026 — 3º e 4º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -957,7 +957,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 18/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 18/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -3855,7 +3855,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
+          <t>Terça, 06/10/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
+          <t>Terça, 06/10/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -3855,7 +3855,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 9º ao 11º tempos</t>
+          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Terça, 06/10/2026 — 9º ao 11º tempos</t>
+          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -2579,17 +2579,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -2599,37 +2599,37 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
+          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -2639,37 +2639,37 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2679,17 +2679,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -2699,17 +2699,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -2719,17 +2719,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -2739,57 +2739,57 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 9º tempo</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 23/09/2026 — 9º tempo</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 19/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -3072,17 +3072,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -3092,37 +3092,37 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
+          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -3132,37 +3132,37 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 6º e 7º tempos</t>
+          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -3172,17 +3172,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -3192,17 +3192,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 11/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -3212,17 +3212,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -3232,17 +3232,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -3252,41 +3252,41 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 11º tempo</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 23/09/2026 — 11º tempo</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -1673,17 +1673,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 9º e 10º tempos</t>
+          <t>Segunda, 14/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -1693,57 +1693,57 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>AG10</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
+          <t>Quinta, 17/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>AG10</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 07/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -2186,17 +2186,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 9º e 10º tempos</t>
+          <t>Segunda, 14/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -2206,57 +2206,57 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>AG10</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
+          <t>Quinta, 17/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>AG10</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 07/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -957,7 +957,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 18/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 18/11/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -1673,17 +1673,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 9º e 10º tempos</t>
+          <t>Segunda, 14/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -1693,57 +1693,57 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>AG10</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
+          <t>Quinta, 17/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>AG10</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 07/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -2186,17 +2186,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 9º e 10º tempos</t>
+          <t>Segunda, 14/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -2206,57 +2206,57 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>AG10</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
+          <t>Quinta, 17/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>AG10</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 08/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 07/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -2579,17 +2579,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -2599,37 +2599,37 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
+          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -2639,37 +2639,37 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2679,17 +2679,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -2699,17 +2699,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -2719,17 +2719,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -2739,57 +2739,57 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 9º tempo</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 28/09/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 23/09/2026 — 9º tempo</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 19/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -3072,17 +3072,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -3092,37 +3092,37 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
+          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -3132,37 +3132,37 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 6º e 7º tempos</t>
+          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -3172,17 +3172,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -3192,17 +3192,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 11/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -3212,17 +3212,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -3232,17 +3232,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 21/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -3252,41 +3252,41 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 23/09/2026 — 11º tempo</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 1º e 2º tempos</t>
+          <t>Quarta, 23/09/2026 — 11º tempo</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -2579,17 +2579,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -2599,17 +2599,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
+          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -2619,57 +2619,57 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
+          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2679,17 +2679,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -3072,17 +3072,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 28/08/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -3192,17 +3192,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -1553,57 +1553,57 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 3º e 4º tempos</t>
+          <t>Segunda, 31/08/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 1º ao 3º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 04/09/2026 — 3º e 4º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -2066,57 +2066,57 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 3º e 4º tempos</t>
+          <t>Segunda, 31/08/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 1º ao 3º tempos</t>
+          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 04/09/2026 — 3º e 4º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -1553,57 +1553,57 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 3º e 4º tempos</t>
+          <t>Segunda, 31/08/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 1º ao 3º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 04/09/2026 — 3º e 4º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -2066,57 +2066,57 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 28/08/2026 — 3º e 4º tempos</t>
+          <t>Segunda, 31/08/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 1º ao 3º tempos</t>
+          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 04/09/2026 — 3º e 4º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -2579,17 +2579,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -2599,17 +2599,17 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 2º e 3º tempos</t>
+          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -2619,57 +2619,57 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
+          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2679,17 +2679,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -3072,17 +3072,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 27/08/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 28/08/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
@@ -3192,17 +3192,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -2609,7 +2609,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 02/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 02/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -19,8 +19,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'9C1'!$A$2:$D$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'9C2'!$A$2:$D$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'10C1'!$A$2:$D$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'10C2'!$A$2:$D$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'10C1'!$A$2:$D$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'10C2'!$A$2:$D$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'11C1'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'11C2'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'12C1'!$A$2:$D$26</definedName>
@@ -1472,7 +1472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1533,57 +1533,57 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 26/08/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 31/08/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 1º ao 3º tempos</t>
+          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 04/09/2026 — 3º e 4º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -1593,17 +1593,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 3º e 4º tempos</t>
+          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -1613,17 +1613,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1633,17 +1633,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1653,17 +1653,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 14/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -1673,17 +1673,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 17/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -1693,57 +1693,57 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>AG10</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>AG10</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
+          <t>Quarta, 07/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -1753,77 +1753,77 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 19/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 1º ao 3º tempos</t>
+          <t>Quarta, 21/10/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 5º tempo</t>
+          <t>Quinta, 22/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 9º e 10º tempos</t>
+          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -1833,57 +1833,57 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 28/10/2026 — 1º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 1º tempo</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -1893,17 +1893,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1913,17 +1913,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 05/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -1933,45 +1933,25 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 2º e 3º tempos</t>
+          <t>Terça, 10/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Mat</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Terça, 10/11/2026 — 10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:D25"/>
+  <autoFilter ref="A2:D24"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -1985,7 +1965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2046,57 +2026,57 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 26/08/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 31/08/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 31/08/2026 — 1º ao 3º tempos</t>
+          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Terça, 01/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 04/09/2026 — 3º e 4º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -2106,17 +2086,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 04/09/2026 — 3º e 4º tempos</t>
+          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -2126,17 +2106,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -2146,17 +2126,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2166,17 +2146,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 14/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -2186,17 +2166,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 17/09/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -2206,57 +2186,57 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>AG10</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>AG10</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 25/09/2026 — 2º ao 7º tempos</t>
+          <t>Quarta, 07/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 07/10/2026 — 2º e 3º tempos</t>
+          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -2266,137 +2246,137 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 19/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 19/10/2026 — 1º ao 3º tempos</t>
+          <t>Quinta, 22/10/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 23/10/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 5º tempo</t>
+          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 28/10/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 7º tempo</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -2406,17 +2386,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Terça, 03/11/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -2426,17 +2406,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º e 3º tempos</t>
+          <t>Terça, 10/11/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -2446,45 +2426,25 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 10º e 11º tempos</t>
+          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Ing</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Quarta, 11/11/2026 — 4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:D25"/>
+  <autoFilter ref="A2:D24"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -2599,17 +2599,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -2619,17 +2619,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2639,17 +2639,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -2659,17 +2659,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -2679,17 +2679,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -2699,17 +2699,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 21/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -3112,17 +3112,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -3132,17 +3132,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -3152,17 +3152,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -3172,17 +3172,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -3192,17 +3192,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -3212,17 +3212,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 21/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -17,8 +17,8 @@
     <sheet name="12C2" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'9C1'!$A$2:$D$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'9C2'!$A$2:$D$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'9C1'!$A$2:$D$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'9C2'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'10C1'!$A$2:$D$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'10C2'!$A$2:$D$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'11C1'!$A$2:$D$25</definedName>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -727,57 +727,57 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Quinta, 24/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -787,17 +787,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Terça, 27/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -807,17 +807,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Terça, 27/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -827,37 +827,37 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º tempo</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 7º tempo</t>
+          <t>Quarta, 04/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -867,37 +867,37 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 05/11/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 06/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -907,65 +907,85 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 13/11/2026 — 5º tempo</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 13/11/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
+          <t>Hist</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
           <t>Mat</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D25" s="5" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D24"/>
+  <autoFilter ref="A2:D25"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -979,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1220,57 +1240,57 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Quinta, 24/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -1280,17 +1300,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Terça, 27/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -1300,17 +1320,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Terça, 27/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -1320,37 +1340,37 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º tempo</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 7º tempo</t>
+          <t>Quarta, 04/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -1360,37 +1380,37 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 05/11/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 06/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -1400,65 +1420,85 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 13/11/2026 — 5º tempo</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 13/11/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
+          <t>Hist</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
           <t>Mat</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D25" s="5" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D24"/>
+  <autoFilter ref="A2:D25"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -17,8 +17,8 @@
     <sheet name="12C2" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'9C1'!$A$2:$D$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'9C2'!$A$2:$D$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'9C1'!$A$2:$D$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'9C2'!$A$2:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'10C1'!$A$2:$D$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'10C2'!$A$2:$D$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'11C1'!$A$2:$D$25</definedName>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -727,57 +727,57 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Quinta, 24/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -787,17 +787,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Terça, 27/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -807,17 +807,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Terça, 27/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -827,37 +827,37 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º tempo</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 7º tempo</t>
+          <t>Quarta, 04/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -867,37 +867,37 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 05/11/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 06/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -907,65 +907,85 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 13/11/2026 — 5º tempo</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 13/11/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
+          <t>Hist</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
           <t>Mat</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D25" s="5" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D24"/>
+  <autoFilter ref="A2:D25"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -979,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1220,57 +1240,57 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>AG9</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
+          <t>Quinta, 24/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>AG9</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 02/10/2026 — 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
+          <t>Quarta, 21/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -1280,17 +1300,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Terça, 27/10/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 22/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
@@ -1300,17 +1320,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
+          <t>Terça, 27/10/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -1320,37 +1340,37 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 2º tempo</t>
+          <t>Quarta, 28/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 05/11/2026 — 7º tempo</t>
+          <t>Quarta, 04/11/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -1360,37 +1380,37 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 06/11/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 05/11/2026 — 7º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 06/11/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -1400,65 +1420,85 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 13/11/2026 — 5º tempo</t>
+          <t>Terça, 10/11/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 13/11/2026 — 5º tempo</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
+          <t>Hist</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Terça, 17/11/2026 — 4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
           <t>Mat</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D25" s="5" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D24"/>
+  <autoFilter ref="A2:D25"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -2599,17 +2639,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -2619,17 +2659,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2639,17 +2679,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -2659,17 +2699,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -2679,17 +2719,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -2699,17 +2739,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 21/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -3112,17 +3152,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 2º e 3º tempos</t>
+          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -3132,17 +3172,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quarta, 09/09/2026 — 6º e 7º tempos</t>
+          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -3152,17 +3192,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 1º e 2º tempos</t>
+          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -3172,17 +3212,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 2º e 3º tempos</t>
+          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -3192,17 +3232,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 16/09/2026 — 4º e 5º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -3212,17 +3252,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
+          <t>Segunda, 21/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -3725,17 +3725,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -3745,17 +3745,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 14/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -3765,17 +3765,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -3785,17 +3785,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -4258,17 +4258,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 10/09/2026 — 4º e 5º tempos</t>
+          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -4278,17 +4278,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
+          <t>Segunda, 14/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -4298,17 +4298,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 14/09/2026 — 4º e 5º tempos</t>
+          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -4318,17 +4318,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Terça, 15/09/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 17/09/2026 — 4º e 5º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -2599,41 +2599,41 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
+          <t>Terça, 08/09/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -3112,41 +3112,41 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 02/09/2026 — 1º e 2º tempos</t>
+          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 03/09/2026 — 9º ao 11º tempos</t>
+          <t>Terça, 08/09/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -3715,7 +3715,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 11º e 12º tempos</t>
+          <t>Terça, 08/09/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 11º e 12º tempos</t>
+          <t>Terça, 08/09/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
